--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_23-10-2025.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_23-10-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£9.93</t>
+          <t>£9.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£9.93</t>
+          <t>£9.90</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -589,27 +589,27 @@
       <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff77359e8e5+80021]
+	GetHandleVerifier [0x0x7ff77359e940+80112]
+	(No symbol) [0x0x7ff77332060f]
+	(No symbol) [0x0x7ff773378854]
+	(No symbol) [0x0x7ff773378b1c]
+	(No symbol) [0x0x7ff7733cc927]
+	(No symbol) [0x0x7ff7733a126f]
+	(No symbol) [0x0x7ff7733c968a]
+	(No symbol) [0x0x7ff7733a1003]
+	(No symbol) [0x0x7ff7733695d1]
+	(No symbol) [0x0x7ff77336a3f3]
+	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
+	GetHandleVerifier [0x0x7ff773857f3a+2936554]
+	GetHandleVerifier [0x0x7ff773878977+3070247]
+	GetHandleVerifier [0x0x7ff7735b83ce+185214]
+	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
+	GetHandleVerifier [0x0x7ff7735a7b24+117460]
+	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
+	GetHandleVerifier [0x0x7ff77358dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -632,7 +632,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -659,17 +659,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£11.27</t>
+          <t>£11.25</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£11.27</t>
+          <t>£11.25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£11.27</t>
+          <t>£11.25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -710,27 +710,27 @@
       <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff77359e8e5+80021]
+	GetHandleVerifier [0x0x7ff77359e940+80112]
+	(No symbol) [0x0x7ff77332060f]
+	(No symbol) [0x0x7ff773378854]
+	(No symbol) [0x0x7ff773378b1c]
+	(No symbol) [0x0x7ff7733cc927]
+	(No symbol) [0x0x7ff7733a126f]
+	(No symbol) [0x0x7ff7733c968a]
+	(No symbol) [0x0x7ff7733a1003]
+	(No symbol) [0x0x7ff7733695d1]
+	(No symbol) [0x0x7ff77336a3f3]
+	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
+	GetHandleVerifier [0x0x7ff773857f3a+2936554]
+	GetHandleVerifier [0x0x7ff773878977+3070247]
+	GetHandleVerifier [0x0x7ff7735b83ce+185214]
+	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
+	GetHandleVerifier [0x0x7ff7735a7b24+117460]
+	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
+	GetHandleVerifier [0x0x7ff77358dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -753,7 +753,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -831,27 +831,27 @@
       <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff77359e8e5+80021]
+	GetHandleVerifier [0x0x7ff77359e940+80112]
+	(No symbol) [0x0x7ff77332060f]
+	(No symbol) [0x0x7ff773378854]
+	(No symbol) [0x0x7ff773378b1c]
+	(No symbol) [0x0x7ff7733cc927]
+	(No symbol) [0x0x7ff7733a126f]
+	(No symbol) [0x0x7ff7733c968a]
+	(No symbol) [0x0x7ff7733a1003]
+	(No symbol) [0x0x7ff7733695d1]
+	(No symbol) [0x0x7ff77336a3f3]
+	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
+	GetHandleVerifier [0x0x7ff773857f3a+2936554]
+	GetHandleVerifier [0x0x7ff773878977+3070247]
+	GetHandleVerifier [0x0x7ff7735b83ce+185214]
+	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
+	GetHandleVerifier [0x0x7ff7735a7b24+117460]
+	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
+	GetHandleVerifier [0x0x7ff77358dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -874,7 +874,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -901,17 +901,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£14.78</t>
+          <t>£14.73</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£14.78</t>
+          <t>£14.73</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£14.78</t>
+          <t>£14.73</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -952,27 +952,27 @@
       <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff77359e8e5+80021]
+	GetHandleVerifier [0x0x7ff77359e940+80112]
+	(No symbol) [0x0x7ff77332060f]
+	(No symbol) [0x0x7ff773378854]
+	(No symbol) [0x0x7ff773378b1c]
+	(No symbol) [0x0x7ff7733cc927]
+	(No symbol) [0x0x7ff7733a126f]
+	(No symbol) [0x0x7ff7733c968a]
+	(No symbol) [0x0x7ff7733a1003]
+	(No symbol) [0x0x7ff7733695d1]
+	(No symbol) [0x0x7ff77336a3f3]
+	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
+	GetHandleVerifier [0x0x7ff773857f3a+2936554]
+	GetHandleVerifier [0x0x7ff773878977+3070247]
+	GetHandleVerifier [0x0x7ff7735b83ce+185214]
+	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
+	GetHandleVerifier [0x0x7ff7735a7b24+117460]
+	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
+	GetHandleVerifier [0x0x7ff77358dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -995,7 +995,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£18.80</t>
+          <t>£18.75</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£18.80</t>
+          <t>£18.75</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£18.80</t>
+          <t>£18.75</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1073,27 +1073,27 @@
       <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff77359e8e5+80021]
+	GetHandleVerifier [0x0x7ff77359e940+80112]
+	(No symbol) [0x0x7ff77332060f]
+	(No symbol) [0x0x7ff773378854]
+	(No symbol) [0x0x7ff773378b1c]
+	(No symbol) [0x0x7ff7733cc927]
+	(No symbol) [0x0x7ff7733a126f]
+	(No symbol) [0x0x7ff7733c968a]
+	(No symbol) [0x0x7ff7733a1003]
+	(No symbol) [0x0x7ff7733695d1]
+	(No symbol) [0x0x7ff77336a3f3]
+	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
+	GetHandleVerifier [0x0x7ff773857f3a+2936554]
+	GetHandleVerifier [0x0x7ff773878977+3070247]
+	GetHandleVerifier [0x0x7ff7735b83ce+185214]
+	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
+	GetHandleVerifier [0x0x7ff7735a7b24+117460]
+	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
+	GetHandleVerifier [0x0x7ff77358dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1194,27 +1194,27 @@
       <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff77359e8e5+80021]
+	GetHandleVerifier [0x0x7ff77359e940+80112]
+	(No symbol) [0x0x7ff77332060f]
+	(No symbol) [0x0x7ff773378854]
+	(No symbol) [0x0x7ff773378b1c]
+	(No symbol) [0x0x7ff7733cc927]
+	(No symbol) [0x0x7ff7733a126f]
+	(No symbol) [0x0x7ff7733c968a]
+	(No symbol) [0x0x7ff7733a1003]
+	(No symbol) [0x0x7ff7733695d1]
+	(No symbol) [0x0x7ff77336a3f3]
+	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
+	GetHandleVerifier [0x0x7ff773857f3a+2936554]
+	GetHandleVerifier [0x0x7ff773878977+3070247]
+	GetHandleVerifier [0x0x7ff7735b83ce+185214]
+	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
+	GetHandleVerifier [0x0x7ff7735a7b24+117460]
+	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
+	GetHandleVerifier [0x0x7ff77358dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1315,27 +1315,27 @@
       <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff77359e8e5+80021]
+	GetHandleVerifier [0x0x7ff77359e940+80112]
+	(No symbol) [0x0x7ff77332060f]
+	(No symbol) [0x0x7ff773378854]
+	(No symbol) [0x0x7ff773378b1c]
+	(No symbol) [0x0x7ff7733cc927]
+	(No symbol) [0x0x7ff7733a126f]
+	(No symbol) [0x0x7ff7733c968a]
+	(No symbol) [0x0x7ff7733a1003]
+	(No symbol) [0x0x7ff7733695d1]
+	(No symbol) [0x0x7ff77336a3f3]
+	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
+	GetHandleVerifier [0x0x7ff773857f3a+2936554]
+	GetHandleVerifier [0x0x7ff773878977+3070247]
+	GetHandleVerifier [0x0x7ff7735b83ce+185214]
+	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
+	GetHandleVerifier [0x0x7ff7735a7b24+117460]
+	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
+	GetHandleVerifier [0x0x7ff77358dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1436,27 +1436,27 @@
       <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff77359e8e5+80021]
+	GetHandleVerifier [0x0x7ff77359e940+80112]
+	(No symbol) [0x0x7ff77332060f]
+	(No symbol) [0x0x7ff773378854]
+	(No symbol) [0x0x7ff773378b1c]
+	(No symbol) [0x0x7ff7733cc927]
+	(No symbol) [0x0x7ff7733a126f]
+	(No symbol) [0x0x7ff7733c968a]
+	(No symbol) [0x0x7ff7733a1003]
+	(No symbol) [0x0x7ff7733695d1]
+	(No symbol) [0x0x7ff77336a3f3]
+	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
+	GetHandleVerifier [0x0x7ff773857f3a+2936554]
+	GetHandleVerifier [0x0x7ff773878977+3070247]
+	GetHandleVerifier [0x0x7ff7735b83ce+185214]
+	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
+	GetHandleVerifier [0x0x7ff7735a7b24+117460]
+	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
+	GetHandleVerifier [0x0x7ff77358dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1557,27 +1557,27 @@
       <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff77359e8e5+80021]
+	GetHandleVerifier [0x0x7ff77359e940+80112]
+	(No symbol) [0x0x7ff77332060f]
+	(No symbol) [0x0x7ff773378854]
+	(No symbol) [0x0x7ff773378b1c]
+	(No symbol) [0x0x7ff7733cc927]
+	(No symbol) [0x0x7ff7733a126f]
+	(No symbol) [0x0x7ff7733c968a]
+	(No symbol) [0x0x7ff7733a1003]
+	(No symbol) [0x0x7ff7733695d1]
+	(No symbol) [0x0x7ff77336a3f3]
+	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
+	GetHandleVerifier [0x0x7ff773857f3a+2936554]
+	GetHandleVerifier [0x0x7ff773878977+3070247]
+	GetHandleVerifier [0x0x7ff7735b83ce+185214]
+	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
+	GetHandleVerifier [0x0x7ff7735a7b24+117460]
+	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
+	GetHandleVerifier [0x0x7ff77358dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1627,17 +1627,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£25.40</t>
+          <t>£25.25</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£25.40</t>
+          <t>£25.25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£25.40</t>
+          <t>£25.25</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1678,27 +1678,27 @@
       <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff77359e8e5+80021]
+	GetHandleVerifier [0x0x7ff77359e940+80112]
+	(No symbol) [0x0x7ff77332060f]
+	(No symbol) [0x0x7ff773378854]
+	(No symbol) [0x0x7ff773378b1c]
+	(No symbol) [0x0x7ff7733cc927]
+	(No symbol) [0x0x7ff7733a126f]
+	(No symbol) [0x0x7ff7733c968a]
+	(No symbol) [0x0x7ff7733a1003]
+	(No symbol) [0x0x7ff7733695d1]
+	(No symbol) [0x0x7ff77336a3f3]
+	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
+	GetHandleVerifier [0x0x7ff773857f3a+2936554]
+	GetHandleVerifier [0x0x7ff773878977+3070247]
+	GetHandleVerifier [0x0x7ff7735b83ce+185214]
+	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
+	GetHandleVerifier [0x0x7ff7735a7b24+117460]
+	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
+	GetHandleVerifier [0x0x7ff77358dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£33.29</t>
+          <t>£33.00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£33.29</t>
+          <t>£33.00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1799,27 +1799,27 @@
       <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff77359e8e5+80021]
+	GetHandleVerifier [0x0x7ff77359e940+80112]
+	(No symbol) [0x0x7ff77332060f]
+	(No symbol) [0x0x7ff773378854]
+	(No symbol) [0x0x7ff773378b1c]
+	(No symbol) [0x0x7ff7733cc927]
+	(No symbol) [0x0x7ff7733a126f]
+	(No symbol) [0x0x7ff7733c968a]
+	(No symbol) [0x0x7ff7733a1003]
+	(No symbol) [0x0x7ff7733695d1]
+	(No symbol) [0x0x7ff77336a3f3]
+	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
+	GetHandleVerifier [0x0x7ff773857f3a+2936554]
+	GetHandleVerifier [0x0x7ff773878977+3070247]
+	GetHandleVerifier [0x0x7ff7735b83ce+185214]
+	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
+	GetHandleVerifier [0x0x7ff7735a7b24+117460]
+	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
+	GetHandleVerifier [0x0x7ff77358dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1869,17 +1869,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£31.10</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£31.10</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£31.10</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1920,27 +1920,27 @@
       <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff77359e8e5+80021]
+	GetHandleVerifier [0x0x7ff77359e940+80112]
+	(No symbol) [0x0x7ff77332060f]
+	(No symbol) [0x0x7ff773378854]
+	(No symbol) [0x0x7ff773378b1c]
+	(No symbol) [0x0x7ff7733cc927]
+	(No symbol) [0x0x7ff7733a126f]
+	(No symbol) [0x0x7ff7733c968a]
+	(No symbol) [0x0x7ff7733a1003]
+	(No symbol) [0x0x7ff7733695d1]
+	(No symbol) [0x0x7ff77336a3f3]
+	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
+	GetHandleVerifier [0x0x7ff773857f3a+2936554]
+	GetHandleVerifier [0x0x7ff773878977+3070247]
+	GetHandleVerifier [0x0x7ff7735b83ce+185214]
+	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
+	GetHandleVerifier [0x0x7ff7735a7b24+117460]
+	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
+	GetHandleVerifier [0x0x7ff77358dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1990,12 +1990,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£39.70</t>
+          <t>£39.45</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£39.70</t>
+          <t>£39.45</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2041,27 +2041,27 @@
       <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff77359e8e5+80021]
+	GetHandleVerifier [0x0x7ff77359e940+80112]
+	(No symbol) [0x0x7ff77332060f]
+	(No symbol) [0x0x7ff773378854]
+	(No symbol) [0x0x7ff773378b1c]
+	(No symbol) [0x0x7ff7733cc927]
+	(No symbol) [0x0x7ff7733a126f]
+	(No symbol) [0x0x7ff7733c968a]
+	(No symbol) [0x0x7ff7733a1003]
+	(No symbol) [0x0x7ff7733695d1]
+	(No symbol) [0x0x7ff77336a3f3]
+	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
+	GetHandleVerifier [0x0x7ff773857f3a+2936554]
+	GetHandleVerifier [0x0x7ff773878977+3070247]
+	GetHandleVerifier [0x0x7ff7735b83ce+185214]
+	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
+	GetHandleVerifier [0x0x7ff7735a7b24+117460]
+	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
+	GetHandleVerifier [0x0x7ff77358dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£38.63</t>
+          <t>£38.30</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£38.63</t>
+          <t>£38.30</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2162,27 +2162,27 @@
       <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff77359e8e5+80021]
+	GetHandleVerifier [0x0x7ff77359e940+80112]
+	(No symbol) [0x0x7ff77332060f]
+	(No symbol) [0x0x7ff773378854]
+	(No symbol) [0x0x7ff773378b1c]
+	(No symbol) [0x0x7ff7733cc927]
+	(No symbol) [0x0x7ff7733a126f]
+	(No symbol) [0x0x7ff7733c968a]
+	(No symbol) [0x0x7ff7733a1003]
+	(No symbol) [0x0x7ff7733695d1]
+	(No symbol) [0x0x7ff77336a3f3]
+	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
+	GetHandleVerifier [0x0x7ff773857f3a+2936554]
+	GetHandleVerifier [0x0x7ff773878977+3070247]
+	GetHandleVerifier [0x0x7ff7735b83ce+185214]
+	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
+	GetHandleVerifier [0x0x7ff7735a7b24+117460]
+	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
+	GetHandleVerifier [0x0x7ff77358dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2232,17 +2232,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£38.10</t>
+          <t>£38.00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£38.10</t>
+          <t>£38.00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£38.10</t>
+          <t>£38.00</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2283,27 +2283,27 @@
       <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff77359e8e5+80021]
+	GetHandleVerifier [0x0x7ff77359e940+80112]
+	(No symbol) [0x0x7ff77332060f]
+	(No symbol) [0x0x7ff773378854]
+	(No symbol) [0x0x7ff773378b1c]
+	(No symbol) [0x0x7ff7733cc927]
+	(No symbol) [0x0x7ff7733a126f]
+	(No symbol) [0x0x7ff7733c968a]
+	(No symbol) [0x0x7ff7733a1003]
+	(No symbol) [0x0x7ff7733695d1]
+	(No symbol) [0x0x7ff77336a3f3]
+	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
+	GetHandleVerifier [0x0x7ff773857f3a+2936554]
+	GetHandleVerifier [0x0x7ff773878977+3070247]
+	GetHandleVerifier [0x0x7ff7735b83ce+185214]
+	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
+	GetHandleVerifier [0x0x7ff7735a7b24+117460]
+	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
+	GetHandleVerifier [0x0x7ff77358dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2501,27 +2501,27 @@
       <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff77359e8e5+80021]
+	GetHandleVerifier [0x0x7ff77359e940+80112]
+	(No symbol) [0x0x7ff77332060f]
+	(No symbol) [0x0x7ff773378854]
+	(No symbol) [0x0x7ff773378b1c]
+	(No symbol) [0x0x7ff7733cc927]
+	(No symbol) [0x0x7ff7733a126f]
+	(No symbol) [0x0x7ff7733c968a]
+	(No symbol) [0x0x7ff7733a1003]
+	(No symbol) [0x0x7ff7733695d1]
+	(No symbol) [0x0x7ff77336a3f3]
+	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
+	GetHandleVerifier [0x0x7ff773857f3a+2936554]
+	GetHandleVerifier [0x0x7ff773878977+3070247]
+	GetHandleVerifier [0x0x7ff7735b83ce+185214]
+	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
+	GetHandleVerifier [0x0x7ff7735a7b24+117460]
+	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
+	GetHandleVerifier [0x0x7ff77358dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2622,27 +2622,27 @@
       <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff77359e8e5+80021]
+	GetHandleVerifier [0x0x7ff77359e940+80112]
+	(No symbol) [0x0x7ff77332060f]
+	(No symbol) [0x0x7ff773378854]
+	(No symbol) [0x0x7ff773378b1c]
+	(No symbol) [0x0x7ff7733cc927]
+	(No symbol) [0x0x7ff7733a126f]
+	(No symbol) [0x0x7ff7733c968a]
+	(No symbol) [0x0x7ff7733a1003]
+	(No symbol) [0x0x7ff7733695d1]
+	(No symbol) [0x0x7ff77336a3f3]
+	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
+	GetHandleVerifier [0x0x7ff773857f3a+2936554]
+	GetHandleVerifier [0x0x7ff773878977+3070247]
+	GetHandleVerifier [0x0x7ff7735b83ce+185214]
+	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
+	GetHandleVerifier [0x0x7ff7735a7b24+117460]
+	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
+	GetHandleVerifier [0x0x7ff77358dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2743,27 +2743,27 @@
       <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff77359e8e5+80021]
+	GetHandleVerifier [0x0x7ff77359e940+80112]
+	(No symbol) [0x0x7ff77332060f]
+	(No symbol) [0x0x7ff773378854]
+	(No symbol) [0x0x7ff773378b1c]
+	(No symbol) [0x0x7ff7733cc927]
+	(No symbol) [0x0x7ff7733a126f]
+	(No symbol) [0x0x7ff7733c968a]
+	(No symbol) [0x0x7ff7733a1003]
+	(No symbol) [0x0x7ff7733695d1]
+	(No symbol) [0x0x7ff77336a3f3]
+	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
+	GetHandleVerifier [0x0x7ff773857f3a+2936554]
+	GetHandleVerifier [0x0x7ff773878977+3070247]
+	GetHandleVerifier [0x0x7ff7735b83ce+185214]
+	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
+	GetHandleVerifier [0x0x7ff7735a7b24+117460]
+	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
+	GetHandleVerifier [0x0x7ff77358dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2864,27 +2864,27 @@
       <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff77359e8e5+80021]
+	GetHandleVerifier [0x0x7ff77359e940+80112]
+	(No symbol) [0x0x7ff77332060f]
+	(No symbol) [0x0x7ff773378854]
+	(No symbol) [0x0x7ff773378b1c]
+	(No symbol) [0x0x7ff7733cc927]
+	(No symbol) [0x0x7ff7733a126f]
+	(No symbol) [0x0x7ff7733c968a]
+	(No symbol) [0x0x7ff7733a1003]
+	(No symbol) [0x0x7ff7733695d1]
+	(No symbol) [0x0x7ff77336a3f3]
+	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
+	GetHandleVerifier [0x0x7ff773857f3a+2936554]
+	GetHandleVerifier [0x0x7ff773878977+3070247]
+	GetHandleVerifier [0x0x7ff7735b83ce+185214]
+	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
+	GetHandleVerifier [0x0x7ff7735a7b24+117460]
+	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
+	GetHandleVerifier [0x0x7ff77358dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2985,27 +2985,27 @@
       <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64d3fe8e5+80021]
-	GetHandleVerifier [0x0x7ff64d3fe940+80112]
-	(No symbol) [0x0x7ff64d18060f]
-	(No symbol) [0x0x7ff64d1d8854]
-	(No symbol) [0x0x7ff64d1d8b1c]
-	(No symbol) [0x0x7ff64d22c927]
-	(No symbol) [0x0x7ff64d20126f]
-	(No symbol) [0x0x7ff64d22968a]
-	(No symbol) [0x0x7ff64d201003]
-	(No symbol) [0x0x7ff64d1c95d1]
-	(No symbol) [0x0x7ff64d1ca3f3]
-	GetHandleVerifier [0x0x7ff64d6bdc7d+2960429]
-	GetHandleVerifier [0x0x7ff64d6b7f3a+2936554]
-	GetHandleVerifier [0x0x7ff64d6d8977+3070247]
-	GetHandleVerifier [0x0x7ff64d4183ce+185214]
-	GetHandleVerifier [0x0x7ff64d41fe1f+216527]
-	GetHandleVerifier [0x0x7ff64d407b24+117460]
-	GetHandleVerifier [0x0x7ff64d407cdf+117903]
-	GetHandleVerifier [0x0x7ff64d3edbb8+11112]
+	GetHandleVerifier [0x0x7ff77359e8e5+80021]
+	GetHandleVerifier [0x0x7ff77359e940+80112]
+	(No symbol) [0x0x7ff77332060f]
+	(No symbol) [0x0x7ff773378854]
+	(No symbol) [0x0x7ff773378b1c]
+	(No symbol) [0x0x7ff7733cc927]
+	(No symbol) [0x0x7ff7733a126f]
+	(No symbol) [0x0x7ff7733c968a]
+	(No symbol) [0x0x7ff7733a1003]
+	(No symbol) [0x0x7ff7733695d1]
+	(No symbol) [0x0x7ff77336a3f3]
+	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
+	GetHandleVerifier [0x0x7ff773857f3a+2936554]
+	GetHandleVerifier [0x0x7ff773878977+3070247]
+	GetHandleVerifier [0x0x7ff7735b83ce+185214]
+	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
+	GetHandleVerifier [0x0x7ff7735a7b24+117460]
+	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
+	GetHandleVerifier [0x0x7ff77358dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">

--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_23-10-2025.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_23-10-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -589,27 +589,27 @@
       <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff77359e8e5+80021]
-	GetHandleVerifier [0x0x7ff77359e940+80112]
-	(No symbol) [0x0x7ff77332060f]
-	(No symbol) [0x0x7ff773378854]
-	(No symbol) [0x0x7ff773378b1c]
-	(No symbol) [0x0x7ff7733cc927]
-	(No symbol) [0x0x7ff7733a126f]
-	(No symbol) [0x0x7ff7733c968a]
-	(No symbol) [0x0x7ff7733a1003]
-	(No symbol) [0x0x7ff7733695d1]
-	(No symbol) [0x0x7ff77336a3f3]
-	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
-	GetHandleVerifier [0x0x7ff773857f3a+2936554]
-	GetHandleVerifier [0x0x7ff773878977+3070247]
-	GetHandleVerifier [0x0x7ff7735b83ce+185214]
-	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
-	GetHandleVerifier [0x0x7ff7735a7b24+117460]
-	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
-	GetHandleVerifier [0x0x7ff77358dbb8+11112]
+	GetHandleVerifier [0x0x7ff64dd7e8e5+80021]
+	GetHandleVerifier [0x0x7ff64dd7e940+80112]
+	(No symbol) [0x0x7ff64db0060f]
+	(No symbol) [0x0x7ff64db58854]
+	(No symbol) [0x0x7ff64db58b1c]
+	(No symbol) [0x0x7ff64dbac927]
+	(No symbol) [0x0x7ff64db8126f]
+	(No symbol) [0x0x7ff64dba968a]
+	(No symbol) [0x0x7ff64db81003]
+	(No symbol) [0x0x7ff64db495d1]
+	(No symbol) [0x0x7ff64db4a3f3]
+	GetHandleVerifier [0x0x7ff64e03dc7d+2960429]
+	GetHandleVerifier [0x0x7ff64e037f3a+2936554]
+	GetHandleVerifier [0x0x7ff64e058977+3070247]
+	GetHandleVerifier [0x0x7ff64dd983ce+185214]
+	GetHandleVerifier [0x0x7ff64dd9fe1f+216527]
+	GetHandleVerifier [0x0x7ff64dd87b24+117460]
+	GetHandleVerifier [0x0x7ff64dd87cdf+117903]
+	GetHandleVerifier [0x0x7ff64dd6dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -632,7 +632,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -710,27 +710,27 @@
       <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff77359e8e5+80021]
-	GetHandleVerifier [0x0x7ff77359e940+80112]
-	(No symbol) [0x0x7ff77332060f]
-	(No symbol) [0x0x7ff773378854]
-	(No symbol) [0x0x7ff773378b1c]
-	(No symbol) [0x0x7ff7733cc927]
-	(No symbol) [0x0x7ff7733a126f]
-	(No symbol) [0x0x7ff7733c968a]
-	(No symbol) [0x0x7ff7733a1003]
-	(No symbol) [0x0x7ff7733695d1]
-	(No symbol) [0x0x7ff77336a3f3]
-	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
-	GetHandleVerifier [0x0x7ff773857f3a+2936554]
-	GetHandleVerifier [0x0x7ff773878977+3070247]
-	GetHandleVerifier [0x0x7ff7735b83ce+185214]
-	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
-	GetHandleVerifier [0x0x7ff7735a7b24+117460]
-	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
-	GetHandleVerifier [0x0x7ff77358dbb8+11112]
+	GetHandleVerifier [0x0x7ff64dd7e8e5+80021]
+	GetHandleVerifier [0x0x7ff64dd7e940+80112]
+	(No symbol) [0x0x7ff64db0060f]
+	(No symbol) [0x0x7ff64db58854]
+	(No symbol) [0x0x7ff64db58b1c]
+	(No symbol) [0x0x7ff64dbac927]
+	(No symbol) [0x0x7ff64db8126f]
+	(No symbol) [0x0x7ff64dba968a]
+	(No symbol) [0x0x7ff64db81003]
+	(No symbol) [0x0x7ff64db495d1]
+	(No symbol) [0x0x7ff64db4a3f3]
+	GetHandleVerifier [0x0x7ff64e03dc7d+2960429]
+	GetHandleVerifier [0x0x7ff64e037f3a+2936554]
+	GetHandleVerifier [0x0x7ff64e058977+3070247]
+	GetHandleVerifier [0x0x7ff64dd983ce+185214]
+	GetHandleVerifier [0x0x7ff64dd9fe1f+216527]
+	GetHandleVerifier [0x0x7ff64dd87b24+117460]
+	GetHandleVerifier [0x0x7ff64dd87cdf+117903]
+	GetHandleVerifier [0x0x7ff64dd6dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -753,7 +753,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -831,27 +831,27 @@
       <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff77359e8e5+80021]
-	GetHandleVerifier [0x0x7ff77359e940+80112]
-	(No symbol) [0x0x7ff77332060f]
-	(No symbol) [0x0x7ff773378854]
-	(No symbol) [0x0x7ff773378b1c]
-	(No symbol) [0x0x7ff7733cc927]
-	(No symbol) [0x0x7ff7733a126f]
-	(No symbol) [0x0x7ff7733c968a]
-	(No symbol) [0x0x7ff7733a1003]
-	(No symbol) [0x0x7ff7733695d1]
-	(No symbol) [0x0x7ff77336a3f3]
-	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
-	GetHandleVerifier [0x0x7ff773857f3a+2936554]
-	GetHandleVerifier [0x0x7ff773878977+3070247]
-	GetHandleVerifier [0x0x7ff7735b83ce+185214]
-	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
-	GetHandleVerifier [0x0x7ff7735a7b24+117460]
-	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
-	GetHandleVerifier [0x0x7ff77358dbb8+11112]
+	GetHandleVerifier [0x0x7ff64dd7e8e5+80021]
+	GetHandleVerifier [0x0x7ff64dd7e940+80112]
+	(No symbol) [0x0x7ff64db0060f]
+	(No symbol) [0x0x7ff64db58854]
+	(No symbol) [0x0x7ff64db58b1c]
+	(No symbol) [0x0x7ff64dbac927]
+	(No symbol) [0x0x7ff64db8126f]
+	(No symbol) [0x0x7ff64dba968a]
+	(No symbol) [0x0x7ff64db81003]
+	(No symbol) [0x0x7ff64db495d1]
+	(No symbol) [0x0x7ff64db4a3f3]
+	GetHandleVerifier [0x0x7ff64e03dc7d+2960429]
+	GetHandleVerifier [0x0x7ff64e037f3a+2936554]
+	GetHandleVerifier [0x0x7ff64e058977+3070247]
+	GetHandleVerifier [0x0x7ff64dd983ce+185214]
+	GetHandleVerifier [0x0x7ff64dd9fe1f+216527]
+	GetHandleVerifier [0x0x7ff64dd87b24+117460]
+	GetHandleVerifier [0x0x7ff64dd87cdf+117903]
+	GetHandleVerifier [0x0x7ff64dd6dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -874,7 +874,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -906,14 +906,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://build4less.co.uk/products/recticel-eurothane-gp-2-4m-x-1-2m-all-sizes?variant=31733178007648</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>£14.73</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>£14.73</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>£16.00-Sale Price old price: £17.50</t>
@@ -952,27 +952,27 @@
       <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff77359e8e5+80021]
-	GetHandleVerifier [0x0x7ff77359e940+80112]
-	(No symbol) [0x0x7ff77332060f]
-	(No symbol) [0x0x7ff773378854]
-	(No symbol) [0x0x7ff773378b1c]
-	(No symbol) [0x0x7ff7733cc927]
-	(No symbol) [0x0x7ff7733a126f]
-	(No symbol) [0x0x7ff7733c968a]
-	(No symbol) [0x0x7ff7733a1003]
-	(No symbol) [0x0x7ff7733695d1]
-	(No symbol) [0x0x7ff77336a3f3]
-	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
-	GetHandleVerifier [0x0x7ff773857f3a+2936554]
-	GetHandleVerifier [0x0x7ff773878977+3070247]
-	GetHandleVerifier [0x0x7ff7735b83ce+185214]
-	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
-	GetHandleVerifier [0x0x7ff7735a7b24+117460]
-	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
-	GetHandleVerifier [0x0x7ff77358dbb8+11112]
+	GetHandleVerifier [0x0x7ff64dd7e8e5+80021]
+	GetHandleVerifier [0x0x7ff64dd7e940+80112]
+	(No symbol) [0x0x7ff64db0060f]
+	(No symbol) [0x0x7ff64db58854]
+	(No symbol) [0x0x7ff64db58b1c]
+	(No symbol) [0x0x7ff64dbac927]
+	(No symbol) [0x0x7ff64db8126f]
+	(No symbol) [0x0x7ff64dba968a]
+	(No symbol) [0x0x7ff64db81003]
+	(No symbol) [0x0x7ff64db495d1]
+	(No symbol) [0x0x7ff64db4a3f3]
+	GetHandleVerifier [0x0x7ff64e03dc7d+2960429]
+	GetHandleVerifier [0x0x7ff64e037f3a+2936554]
+	GetHandleVerifier [0x0x7ff64e058977+3070247]
+	GetHandleVerifier [0x0x7ff64dd983ce+185214]
+	GetHandleVerifier [0x0x7ff64dd9fe1f+216527]
+	GetHandleVerifier [0x0x7ff64dd87b24+117460]
+	GetHandleVerifier [0x0x7ff64dd87cdf+117903]
+	GetHandleVerifier [0x0x7ff64dd6dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -995,7 +995,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1073,27 +1073,27 @@
       <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff77359e8e5+80021]
-	GetHandleVerifier [0x0x7ff77359e940+80112]
-	(No symbol) [0x0x7ff77332060f]
-	(No symbol) [0x0x7ff773378854]
-	(No symbol) [0x0x7ff773378b1c]
-	(No symbol) [0x0x7ff7733cc927]
-	(No symbol) [0x0x7ff7733a126f]
-	(No symbol) [0x0x7ff7733c968a]
-	(No symbol) [0x0x7ff7733a1003]
-	(No symbol) [0x0x7ff7733695d1]
-	(No symbol) [0x0x7ff77336a3f3]
-	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
-	GetHandleVerifier [0x0x7ff773857f3a+2936554]
-	GetHandleVerifier [0x0x7ff773878977+3070247]
-	GetHandleVerifier [0x0x7ff7735b83ce+185214]
-	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
-	GetHandleVerifier [0x0x7ff7735a7b24+117460]
-	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
-	GetHandleVerifier [0x0x7ff77358dbb8+11112]
+	GetHandleVerifier [0x0x7ff64dd7e8e5+80021]
+	GetHandleVerifier [0x0x7ff64dd7e940+80112]
+	(No symbol) [0x0x7ff64db0060f]
+	(No symbol) [0x0x7ff64db58854]
+	(No symbol) [0x0x7ff64db58b1c]
+	(No symbol) [0x0x7ff64dbac927]
+	(No symbol) [0x0x7ff64db8126f]
+	(No symbol) [0x0x7ff64dba968a]
+	(No symbol) [0x0x7ff64db81003]
+	(No symbol) [0x0x7ff64db495d1]
+	(No symbol) [0x0x7ff64db4a3f3]
+	GetHandleVerifier [0x0x7ff64e03dc7d+2960429]
+	GetHandleVerifier [0x0x7ff64e037f3a+2936554]
+	GetHandleVerifier [0x0x7ff64e058977+3070247]
+	GetHandleVerifier [0x0x7ff64dd983ce+185214]
+	GetHandleVerifier [0x0x7ff64dd9fe1f+216527]
+	GetHandleVerifier [0x0x7ff64dd87b24+117460]
+	GetHandleVerifier [0x0x7ff64dd87cdf+117903]
+	GetHandleVerifier [0x0x7ff64dd6dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1194,27 +1194,27 @@
       <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff77359e8e5+80021]
-	GetHandleVerifier [0x0x7ff77359e940+80112]
-	(No symbol) [0x0x7ff77332060f]
-	(No symbol) [0x0x7ff773378854]
-	(No symbol) [0x0x7ff773378b1c]
-	(No symbol) [0x0x7ff7733cc927]
-	(No symbol) [0x0x7ff7733a126f]
-	(No symbol) [0x0x7ff7733c968a]
-	(No symbol) [0x0x7ff7733a1003]
-	(No symbol) [0x0x7ff7733695d1]
-	(No symbol) [0x0x7ff77336a3f3]
-	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
-	GetHandleVerifier [0x0x7ff773857f3a+2936554]
-	GetHandleVerifier [0x0x7ff773878977+3070247]
-	GetHandleVerifier [0x0x7ff7735b83ce+185214]
-	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
-	GetHandleVerifier [0x0x7ff7735a7b24+117460]
-	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
-	GetHandleVerifier [0x0x7ff77358dbb8+11112]
+	GetHandleVerifier [0x0x7ff64dd7e8e5+80021]
+	GetHandleVerifier [0x0x7ff64dd7e940+80112]
+	(No symbol) [0x0x7ff64db0060f]
+	(No symbol) [0x0x7ff64db58854]
+	(No symbol) [0x0x7ff64db58b1c]
+	(No symbol) [0x0x7ff64dbac927]
+	(No symbol) [0x0x7ff64db8126f]
+	(No symbol) [0x0x7ff64dba968a]
+	(No symbol) [0x0x7ff64db81003]
+	(No symbol) [0x0x7ff64db495d1]
+	(No symbol) [0x0x7ff64db4a3f3]
+	GetHandleVerifier [0x0x7ff64e03dc7d+2960429]
+	GetHandleVerifier [0x0x7ff64e037f3a+2936554]
+	GetHandleVerifier [0x0x7ff64e058977+3070247]
+	GetHandleVerifier [0x0x7ff64dd983ce+185214]
+	GetHandleVerifier [0x0x7ff64dd9fe1f+216527]
+	GetHandleVerifier [0x0x7ff64dd87b24+117460]
+	GetHandleVerifier [0x0x7ff64dd87cdf+117903]
+	GetHandleVerifier [0x0x7ff64dd6dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1315,27 +1315,27 @@
       <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff77359e8e5+80021]
-	GetHandleVerifier [0x0x7ff77359e940+80112]
-	(No symbol) [0x0x7ff77332060f]
-	(No symbol) [0x0x7ff773378854]
-	(No symbol) [0x0x7ff773378b1c]
-	(No symbol) [0x0x7ff7733cc927]
-	(No symbol) [0x0x7ff7733a126f]
-	(No symbol) [0x0x7ff7733c968a]
-	(No symbol) [0x0x7ff7733a1003]
-	(No symbol) [0x0x7ff7733695d1]
-	(No symbol) [0x0x7ff77336a3f3]
-	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
-	GetHandleVerifier [0x0x7ff773857f3a+2936554]
-	GetHandleVerifier [0x0x7ff773878977+3070247]
-	GetHandleVerifier [0x0x7ff7735b83ce+185214]
-	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
-	GetHandleVerifier [0x0x7ff7735a7b24+117460]
-	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
-	GetHandleVerifier [0x0x7ff77358dbb8+11112]
+	GetHandleVerifier [0x0x7ff64dd7e8e5+80021]
+	GetHandleVerifier [0x0x7ff64dd7e940+80112]
+	(No symbol) [0x0x7ff64db0060f]
+	(No symbol) [0x0x7ff64db58854]
+	(No symbol) [0x0x7ff64db58b1c]
+	(No symbol) [0x0x7ff64dbac927]
+	(No symbol) [0x0x7ff64db8126f]
+	(No symbol) [0x0x7ff64dba968a]
+	(No symbol) [0x0x7ff64db81003]
+	(No symbol) [0x0x7ff64db495d1]
+	(No symbol) [0x0x7ff64db4a3f3]
+	GetHandleVerifier [0x0x7ff64e03dc7d+2960429]
+	GetHandleVerifier [0x0x7ff64e037f3a+2936554]
+	GetHandleVerifier [0x0x7ff64e058977+3070247]
+	GetHandleVerifier [0x0x7ff64dd983ce+185214]
+	GetHandleVerifier [0x0x7ff64dd9fe1f+216527]
+	GetHandleVerifier [0x0x7ff64dd87b24+117460]
+	GetHandleVerifier [0x0x7ff64dd87cdf+117903]
+	GetHandleVerifier [0x0x7ff64dd6dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1436,27 +1436,27 @@
       <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff77359e8e5+80021]
-	GetHandleVerifier [0x0x7ff77359e940+80112]
-	(No symbol) [0x0x7ff77332060f]
-	(No symbol) [0x0x7ff773378854]
-	(No symbol) [0x0x7ff773378b1c]
-	(No symbol) [0x0x7ff7733cc927]
-	(No symbol) [0x0x7ff7733a126f]
-	(No symbol) [0x0x7ff7733c968a]
-	(No symbol) [0x0x7ff7733a1003]
-	(No symbol) [0x0x7ff7733695d1]
-	(No symbol) [0x0x7ff77336a3f3]
-	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
-	GetHandleVerifier [0x0x7ff773857f3a+2936554]
-	GetHandleVerifier [0x0x7ff773878977+3070247]
-	GetHandleVerifier [0x0x7ff7735b83ce+185214]
-	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
-	GetHandleVerifier [0x0x7ff7735a7b24+117460]
-	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
-	GetHandleVerifier [0x0x7ff77358dbb8+11112]
+	GetHandleVerifier [0x0x7ff64dd7e8e5+80021]
+	GetHandleVerifier [0x0x7ff64dd7e940+80112]
+	(No symbol) [0x0x7ff64db0060f]
+	(No symbol) [0x0x7ff64db58854]
+	(No symbol) [0x0x7ff64db58b1c]
+	(No symbol) [0x0x7ff64dbac927]
+	(No symbol) [0x0x7ff64db8126f]
+	(No symbol) [0x0x7ff64dba968a]
+	(No symbol) [0x0x7ff64db81003]
+	(No symbol) [0x0x7ff64db495d1]
+	(No symbol) [0x0x7ff64db4a3f3]
+	GetHandleVerifier [0x0x7ff64e03dc7d+2960429]
+	GetHandleVerifier [0x0x7ff64e037f3a+2936554]
+	GetHandleVerifier [0x0x7ff64e058977+3070247]
+	GetHandleVerifier [0x0x7ff64dd983ce+185214]
+	GetHandleVerifier [0x0x7ff64dd9fe1f+216527]
+	GetHandleVerifier [0x0x7ff64dd87b24+117460]
+	GetHandleVerifier [0x0x7ff64dd87cdf+117903]
+	GetHandleVerifier [0x0x7ff64dd6dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1557,27 +1557,27 @@
       <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff77359e8e5+80021]
-	GetHandleVerifier [0x0x7ff77359e940+80112]
-	(No symbol) [0x0x7ff77332060f]
-	(No symbol) [0x0x7ff773378854]
-	(No symbol) [0x0x7ff773378b1c]
-	(No symbol) [0x0x7ff7733cc927]
-	(No symbol) [0x0x7ff7733a126f]
-	(No symbol) [0x0x7ff7733c968a]
-	(No symbol) [0x0x7ff7733a1003]
-	(No symbol) [0x0x7ff7733695d1]
-	(No symbol) [0x0x7ff77336a3f3]
-	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
-	GetHandleVerifier [0x0x7ff773857f3a+2936554]
-	GetHandleVerifier [0x0x7ff773878977+3070247]
-	GetHandleVerifier [0x0x7ff7735b83ce+185214]
-	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
-	GetHandleVerifier [0x0x7ff7735a7b24+117460]
-	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
-	GetHandleVerifier [0x0x7ff77358dbb8+11112]
+	GetHandleVerifier [0x0x7ff64dd7e8e5+80021]
+	GetHandleVerifier [0x0x7ff64dd7e940+80112]
+	(No symbol) [0x0x7ff64db0060f]
+	(No symbol) [0x0x7ff64db58854]
+	(No symbol) [0x0x7ff64db58b1c]
+	(No symbol) [0x0x7ff64dbac927]
+	(No symbol) [0x0x7ff64db8126f]
+	(No symbol) [0x0x7ff64dba968a]
+	(No symbol) [0x0x7ff64db81003]
+	(No symbol) [0x0x7ff64db495d1]
+	(No symbol) [0x0x7ff64db4a3f3]
+	GetHandleVerifier [0x0x7ff64e03dc7d+2960429]
+	GetHandleVerifier [0x0x7ff64e037f3a+2936554]
+	GetHandleVerifier [0x0x7ff64e058977+3070247]
+	GetHandleVerifier [0x0x7ff64dd983ce+185214]
+	GetHandleVerifier [0x0x7ff64dd9fe1f+216527]
+	GetHandleVerifier [0x0x7ff64dd87b24+117460]
+	GetHandleVerifier [0x0x7ff64dd87cdf+117903]
+	GetHandleVerifier [0x0x7ff64dd6dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1678,27 +1678,27 @@
       <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff77359e8e5+80021]
-	GetHandleVerifier [0x0x7ff77359e940+80112]
-	(No symbol) [0x0x7ff77332060f]
-	(No symbol) [0x0x7ff773378854]
-	(No symbol) [0x0x7ff773378b1c]
-	(No symbol) [0x0x7ff7733cc927]
-	(No symbol) [0x0x7ff7733a126f]
-	(No symbol) [0x0x7ff7733c968a]
-	(No symbol) [0x0x7ff7733a1003]
-	(No symbol) [0x0x7ff7733695d1]
-	(No symbol) [0x0x7ff77336a3f3]
-	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
-	GetHandleVerifier [0x0x7ff773857f3a+2936554]
-	GetHandleVerifier [0x0x7ff773878977+3070247]
-	GetHandleVerifier [0x0x7ff7735b83ce+185214]
-	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
-	GetHandleVerifier [0x0x7ff7735a7b24+117460]
-	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
-	GetHandleVerifier [0x0x7ff77358dbb8+11112]
+	GetHandleVerifier [0x0x7ff64dd7e8e5+80021]
+	GetHandleVerifier [0x0x7ff64dd7e940+80112]
+	(No symbol) [0x0x7ff64db0060f]
+	(No symbol) [0x0x7ff64db58854]
+	(No symbol) [0x0x7ff64db58b1c]
+	(No symbol) [0x0x7ff64dbac927]
+	(No symbol) [0x0x7ff64db8126f]
+	(No symbol) [0x0x7ff64dba968a]
+	(No symbol) [0x0x7ff64db81003]
+	(No symbol) [0x0x7ff64db495d1]
+	(No symbol) [0x0x7ff64db4a3f3]
+	GetHandleVerifier [0x0x7ff64e03dc7d+2960429]
+	GetHandleVerifier [0x0x7ff64e037f3a+2936554]
+	GetHandleVerifier [0x0x7ff64e058977+3070247]
+	GetHandleVerifier [0x0x7ff64dd983ce+185214]
+	GetHandleVerifier [0x0x7ff64dd9fe1f+216527]
+	GetHandleVerifier [0x0x7ff64dd87b24+117460]
+	GetHandleVerifier [0x0x7ff64dd87cdf+117903]
+	GetHandleVerifier [0x0x7ff64dd6dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1799,27 +1799,27 @@
       <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff77359e8e5+80021]
-	GetHandleVerifier [0x0x7ff77359e940+80112]
-	(No symbol) [0x0x7ff77332060f]
-	(No symbol) [0x0x7ff773378854]
-	(No symbol) [0x0x7ff773378b1c]
-	(No symbol) [0x0x7ff7733cc927]
-	(No symbol) [0x0x7ff7733a126f]
-	(No symbol) [0x0x7ff7733c968a]
-	(No symbol) [0x0x7ff7733a1003]
-	(No symbol) [0x0x7ff7733695d1]
-	(No symbol) [0x0x7ff77336a3f3]
-	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
-	GetHandleVerifier [0x0x7ff773857f3a+2936554]
-	GetHandleVerifier [0x0x7ff773878977+3070247]
-	GetHandleVerifier [0x0x7ff7735b83ce+185214]
-	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
-	GetHandleVerifier [0x0x7ff7735a7b24+117460]
-	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
-	GetHandleVerifier [0x0x7ff77358dbb8+11112]
+	GetHandleVerifier [0x0x7ff64dd7e8e5+80021]
+	GetHandleVerifier [0x0x7ff64dd7e940+80112]
+	(No symbol) [0x0x7ff64db0060f]
+	(No symbol) [0x0x7ff64db58854]
+	(No symbol) [0x0x7ff64db58b1c]
+	(No symbol) [0x0x7ff64dbac927]
+	(No symbol) [0x0x7ff64db8126f]
+	(No symbol) [0x0x7ff64dba968a]
+	(No symbol) [0x0x7ff64db81003]
+	(No symbol) [0x0x7ff64db495d1]
+	(No symbol) [0x0x7ff64db4a3f3]
+	GetHandleVerifier [0x0x7ff64e03dc7d+2960429]
+	GetHandleVerifier [0x0x7ff64e037f3a+2936554]
+	GetHandleVerifier [0x0x7ff64e058977+3070247]
+	GetHandleVerifier [0x0x7ff64dd983ce+185214]
+	GetHandleVerifier [0x0x7ff64dd9fe1f+216527]
+	GetHandleVerifier [0x0x7ff64dd87b24+117460]
+	GetHandleVerifier [0x0x7ff64dd87cdf+117903]
+	GetHandleVerifier [0x0x7ff64dd6dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1920,27 +1920,27 @@
       <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff77359e8e5+80021]
-	GetHandleVerifier [0x0x7ff77359e940+80112]
-	(No symbol) [0x0x7ff77332060f]
-	(No symbol) [0x0x7ff773378854]
-	(No symbol) [0x0x7ff773378b1c]
-	(No symbol) [0x0x7ff7733cc927]
-	(No symbol) [0x0x7ff7733a126f]
-	(No symbol) [0x0x7ff7733c968a]
-	(No symbol) [0x0x7ff7733a1003]
-	(No symbol) [0x0x7ff7733695d1]
-	(No symbol) [0x0x7ff77336a3f3]
-	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
-	GetHandleVerifier [0x0x7ff773857f3a+2936554]
-	GetHandleVerifier [0x0x7ff773878977+3070247]
-	GetHandleVerifier [0x0x7ff7735b83ce+185214]
-	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
-	GetHandleVerifier [0x0x7ff7735a7b24+117460]
-	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
-	GetHandleVerifier [0x0x7ff77358dbb8+11112]
+	GetHandleVerifier [0x0x7ff64dd7e8e5+80021]
+	GetHandleVerifier [0x0x7ff64dd7e940+80112]
+	(No symbol) [0x0x7ff64db0060f]
+	(No symbol) [0x0x7ff64db58854]
+	(No symbol) [0x0x7ff64db58b1c]
+	(No symbol) [0x0x7ff64dbac927]
+	(No symbol) [0x0x7ff64db8126f]
+	(No symbol) [0x0x7ff64dba968a]
+	(No symbol) [0x0x7ff64db81003]
+	(No symbol) [0x0x7ff64db495d1]
+	(No symbol) [0x0x7ff64db4a3f3]
+	GetHandleVerifier [0x0x7ff64e03dc7d+2960429]
+	GetHandleVerifier [0x0x7ff64e037f3a+2936554]
+	GetHandleVerifier [0x0x7ff64e058977+3070247]
+	GetHandleVerifier [0x0x7ff64dd983ce+185214]
+	GetHandleVerifier [0x0x7ff64dd9fe1f+216527]
+	GetHandleVerifier [0x0x7ff64dd87b24+117460]
+	GetHandleVerifier [0x0x7ff64dd87cdf+117903]
+	GetHandleVerifier [0x0x7ff64dd6dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -2041,27 +2041,27 @@
       <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff77359e8e5+80021]
-	GetHandleVerifier [0x0x7ff77359e940+80112]
-	(No symbol) [0x0x7ff77332060f]
-	(No symbol) [0x0x7ff773378854]
-	(No symbol) [0x0x7ff773378b1c]
-	(No symbol) [0x0x7ff7733cc927]
-	(No symbol) [0x0x7ff7733a126f]
-	(No symbol) [0x0x7ff7733c968a]
-	(No symbol) [0x0x7ff7733a1003]
-	(No symbol) [0x0x7ff7733695d1]
-	(No symbol) [0x0x7ff77336a3f3]
-	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
-	GetHandleVerifier [0x0x7ff773857f3a+2936554]
-	GetHandleVerifier [0x0x7ff773878977+3070247]
-	GetHandleVerifier [0x0x7ff7735b83ce+185214]
-	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
-	GetHandleVerifier [0x0x7ff7735a7b24+117460]
-	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
-	GetHandleVerifier [0x0x7ff77358dbb8+11112]
+	GetHandleVerifier [0x0x7ff64dd7e8e5+80021]
+	GetHandleVerifier [0x0x7ff64dd7e940+80112]
+	(No symbol) [0x0x7ff64db0060f]
+	(No symbol) [0x0x7ff64db58854]
+	(No symbol) [0x0x7ff64db58b1c]
+	(No symbol) [0x0x7ff64dbac927]
+	(No symbol) [0x0x7ff64db8126f]
+	(No symbol) [0x0x7ff64dba968a]
+	(No symbol) [0x0x7ff64db81003]
+	(No symbol) [0x0x7ff64db495d1]
+	(No symbol) [0x0x7ff64db4a3f3]
+	GetHandleVerifier [0x0x7ff64e03dc7d+2960429]
+	GetHandleVerifier [0x0x7ff64e037f3a+2936554]
+	GetHandleVerifier [0x0x7ff64e058977+3070247]
+	GetHandleVerifier [0x0x7ff64dd983ce+185214]
+	GetHandleVerifier [0x0x7ff64dd9fe1f+216527]
+	GetHandleVerifier [0x0x7ff64dd87b24+117460]
+	GetHandleVerifier [0x0x7ff64dd87cdf+117903]
+	GetHandleVerifier [0x0x7ff64dd6dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2162,27 +2162,27 @@
       <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff77359e8e5+80021]
-	GetHandleVerifier [0x0x7ff77359e940+80112]
-	(No symbol) [0x0x7ff77332060f]
-	(No symbol) [0x0x7ff773378854]
-	(No symbol) [0x0x7ff773378b1c]
-	(No symbol) [0x0x7ff7733cc927]
-	(No symbol) [0x0x7ff7733a126f]
-	(No symbol) [0x0x7ff7733c968a]
-	(No symbol) [0x0x7ff7733a1003]
-	(No symbol) [0x0x7ff7733695d1]
-	(No symbol) [0x0x7ff77336a3f3]
-	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
-	GetHandleVerifier [0x0x7ff773857f3a+2936554]
-	GetHandleVerifier [0x0x7ff773878977+3070247]
-	GetHandleVerifier [0x0x7ff7735b83ce+185214]
-	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
-	GetHandleVerifier [0x0x7ff7735a7b24+117460]
-	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
-	GetHandleVerifier [0x0x7ff77358dbb8+11112]
+	GetHandleVerifier [0x0x7ff64dd7e8e5+80021]
+	GetHandleVerifier [0x0x7ff64dd7e940+80112]
+	(No symbol) [0x0x7ff64db0060f]
+	(No symbol) [0x0x7ff64db58854]
+	(No symbol) [0x0x7ff64db58b1c]
+	(No symbol) [0x0x7ff64dbac927]
+	(No symbol) [0x0x7ff64db8126f]
+	(No symbol) [0x0x7ff64dba968a]
+	(No symbol) [0x0x7ff64db81003]
+	(No symbol) [0x0x7ff64db495d1]
+	(No symbol) [0x0x7ff64db4a3f3]
+	GetHandleVerifier [0x0x7ff64e03dc7d+2960429]
+	GetHandleVerifier [0x0x7ff64e037f3a+2936554]
+	GetHandleVerifier [0x0x7ff64e058977+3070247]
+	GetHandleVerifier [0x0x7ff64dd983ce+185214]
+	GetHandleVerifier [0x0x7ff64dd9fe1f+216527]
+	GetHandleVerifier [0x0x7ff64dd87b24+117460]
+	GetHandleVerifier [0x0x7ff64dd87cdf+117903]
+	GetHandleVerifier [0x0x7ff64dd6dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2283,27 +2283,27 @@
       <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff77359e8e5+80021]
-	GetHandleVerifier [0x0x7ff77359e940+80112]
-	(No symbol) [0x0x7ff77332060f]
-	(No symbol) [0x0x7ff773378854]
-	(No symbol) [0x0x7ff773378b1c]
-	(No symbol) [0x0x7ff7733cc927]
-	(No symbol) [0x0x7ff7733a126f]
-	(No symbol) [0x0x7ff7733c968a]
-	(No symbol) [0x0x7ff7733a1003]
-	(No symbol) [0x0x7ff7733695d1]
-	(No symbol) [0x0x7ff77336a3f3]
-	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
-	GetHandleVerifier [0x0x7ff773857f3a+2936554]
-	GetHandleVerifier [0x0x7ff773878977+3070247]
-	GetHandleVerifier [0x0x7ff7735b83ce+185214]
-	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
-	GetHandleVerifier [0x0x7ff7735a7b24+117460]
-	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
-	GetHandleVerifier [0x0x7ff77358dbb8+11112]
+	GetHandleVerifier [0x0x7ff64dd7e8e5+80021]
+	GetHandleVerifier [0x0x7ff64dd7e940+80112]
+	(No symbol) [0x0x7ff64db0060f]
+	(No symbol) [0x0x7ff64db58854]
+	(No symbol) [0x0x7ff64db58b1c]
+	(No symbol) [0x0x7ff64dbac927]
+	(No symbol) [0x0x7ff64db8126f]
+	(No symbol) [0x0x7ff64dba968a]
+	(No symbol) [0x0x7ff64db81003]
+	(No symbol) [0x0x7ff64db495d1]
+	(No symbol) [0x0x7ff64db4a3f3]
+	GetHandleVerifier [0x0x7ff64e03dc7d+2960429]
+	GetHandleVerifier [0x0x7ff64e037f3a+2936554]
+	GetHandleVerifier [0x0x7ff64e058977+3070247]
+	GetHandleVerifier [0x0x7ff64dd983ce+185214]
+	GetHandleVerifier [0x0x7ff64dd9fe1f+216527]
+	GetHandleVerifier [0x0x7ff64dd87b24+117460]
+	GetHandleVerifier [0x0x7ff64dd87cdf+117903]
+	GetHandleVerifier [0x0x7ff64dd6dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2501,27 +2501,27 @@
       <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff77359e8e5+80021]
-	GetHandleVerifier [0x0x7ff77359e940+80112]
-	(No symbol) [0x0x7ff77332060f]
-	(No symbol) [0x0x7ff773378854]
-	(No symbol) [0x0x7ff773378b1c]
-	(No symbol) [0x0x7ff7733cc927]
-	(No symbol) [0x0x7ff7733a126f]
-	(No symbol) [0x0x7ff7733c968a]
-	(No symbol) [0x0x7ff7733a1003]
-	(No symbol) [0x0x7ff7733695d1]
-	(No symbol) [0x0x7ff77336a3f3]
-	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
-	GetHandleVerifier [0x0x7ff773857f3a+2936554]
-	GetHandleVerifier [0x0x7ff773878977+3070247]
-	GetHandleVerifier [0x0x7ff7735b83ce+185214]
-	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
-	GetHandleVerifier [0x0x7ff7735a7b24+117460]
-	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
-	GetHandleVerifier [0x0x7ff77358dbb8+11112]
+	GetHandleVerifier [0x0x7ff64dd7e8e5+80021]
+	GetHandleVerifier [0x0x7ff64dd7e940+80112]
+	(No symbol) [0x0x7ff64db0060f]
+	(No symbol) [0x0x7ff64db58854]
+	(No symbol) [0x0x7ff64db58b1c]
+	(No symbol) [0x0x7ff64dbac927]
+	(No symbol) [0x0x7ff64db8126f]
+	(No symbol) [0x0x7ff64dba968a]
+	(No symbol) [0x0x7ff64db81003]
+	(No symbol) [0x0x7ff64db495d1]
+	(No symbol) [0x0x7ff64db4a3f3]
+	GetHandleVerifier [0x0x7ff64e03dc7d+2960429]
+	GetHandleVerifier [0x0x7ff64e037f3a+2936554]
+	GetHandleVerifier [0x0x7ff64e058977+3070247]
+	GetHandleVerifier [0x0x7ff64dd983ce+185214]
+	GetHandleVerifier [0x0x7ff64dd9fe1f+216527]
+	GetHandleVerifier [0x0x7ff64dd87b24+117460]
+	GetHandleVerifier [0x0x7ff64dd87cdf+117903]
+	GetHandleVerifier [0x0x7ff64dd6dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2622,27 +2622,27 @@
       <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff77359e8e5+80021]
-	GetHandleVerifier [0x0x7ff77359e940+80112]
-	(No symbol) [0x0x7ff77332060f]
-	(No symbol) [0x0x7ff773378854]
-	(No symbol) [0x0x7ff773378b1c]
-	(No symbol) [0x0x7ff7733cc927]
-	(No symbol) [0x0x7ff7733a126f]
-	(No symbol) [0x0x7ff7733c968a]
-	(No symbol) [0x0x7ff7733a1003]
-	(No symbol) [0x0x7ff7733695d1]
-	(No symbol) [0x0x7ff77336a3f3]
-	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
-	GetHandleVerifier [0x0x7ff773857f3a+2936554]
-	GetHandleVerifier [0x0x7ff773878977+3070247]
-	GetHandleVerifier [0x0x7ff7735b83ce+185214]
-	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
-	GetHandleVerifier [0x0x7ff7735a7b24+117460]
-	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
-	GetHandleVerifier [0x0x7ff77358dbb8+11112]
+	GetHandleVerifier [0x0x7ff64dd7e8e5+80021]
+	GetHandleVerifier [0x0x7ff64dd7e940+80112]
+	(No symbol) [0x0x7ff64db0060f]
+	(No symbol) [0x0x7ff64db58854]
+	(No symbol) [0x0x7ff64db58b1c]
+	(No symbol) [0x0x7ff64dbac927]
+	(No symbol) [0x0x7ff64db8126f]
+	(No symbol) [0x0x7ff64dba968a]
+	(No symbol) [0x0x7ff64db81003]
+	(No symbol) [0x0x7ff64db495d1]
+	(No symbol) [0x0x7ff64db4a3f3]
+	GetHandleVerifier [0x0x7ff64e03dc7d+2960429]
+	GetHandleVerifier [0x0x7ff64e037f3a+2936554]
+	GetHandleVerifier [0x0x7ff64e058977+3070247]
+	GetHandleVerifier [0x0x7ff64dd983ce+185214]
+	GetHandleVerifier [0x0x7ff64dd9fe1f+216527]
+	GetHandleVerifier [0x0x7ff64dd87b24+117460]
+	GetHandleVerifier [0x0x7ff64dd87cdf+117903]
+	GetHandleVerifier [0x0x7ff64dd6dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2743,27 +2743,27 @@
       <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff77359e8e5+80021]
-	GetHandleVerifier [0x0x7ff77359e940+80112]
-	(No symbol) [0x0x7ff77332060f]
-	(No symbol) [0x0x7ff773378854]
-	(No symbol) [0x0x7ff773378b1c]
-	(No symbol) [0x0x7ff7733cc927]
-	(No symbol) [0x0x7ff7733a126f]
-	(No symbol) [0x0x7ff7733c968a]
-	(No symbol) [0x0x7ff7733a1003]
-	(No symbol) [0x0x7ff7733695d1]
-	(No symbol) [0x0x7ff77336a3f3]
-	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
-	GetHandleVerifier [0x0x7ff773857f3a+2936554]
-	GetHandleVerifier [0x0x7ff773878977+3070247]
-	GetHandleVerifier [0x0x7ff7735b83ce+185214]
-	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
-	GetHandleVerifier [0x0x7ff7735a7b24+117460]
-	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
-	GetHandleVerifier [0x0x7ff77358dbb8+11112]
+	GetHandleVerifier [0x0x7ff64dd7e8e5+80021]
+	GetHandleVerifier [0x0x7ff64dd7e940+80112]
+	(No symbol) [0x0x7ff64db0060f]
+	(No symbol) [0x0x7ff64db58854]
+	(No symbol) [0x0x7ff64db58b1c]
+	(No symbol) [0x0x7ff64dbac927]
+	(No symbol) [0x0x7ff64db8126f]
+	(No symbol) [0x0x7ff64dba968a]
+	(No symbol) [0x0x7ff64db81003]
+	(No symbol) [0x0x7ff64db495d1]
+	(No symbol) [0x0x7ff64db4a3f3]
+	GetHandleVerifier [0x0x7ff64e03dc7d+2960429]
+	GetHandleVerifier [0x0x7ff64e037f3a+2936554]
+	GetHandleVerifier [0x0x7ff64e058977+3070247]
+	GetHandleVerifier [0x0x7ff64dd983ce+185214]
+	GetHandleVerifier [0x0x7ff64dd9fe1f+216527]
+	GetHandleVerifier [0x0x7ff64dd87b24+117460]
+	GetHandleVerifier [0x0x7ff64dd87cdf+117903]
+	GetHandleVerifier [0x0x7ff64dd6dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2864,27 +2864,27 @@
       <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff77359e8e5+80021]
-	GetHandleVerifier [0x0x7ff77359e940+80112]
-	(No symbol) [0x0x7ff77332060f]
-	(No symbol) [0x0x7ff773378854]
-	(No symbol) [0x0x7ff773378b1c]
-	(No symbol) [0x0x7ff7733cc927]
-	(No symbol) [0x0x7ff7733a126f]
-	(No symbol) [0x0x7ff7733c968a]
-	(No symbol) [0x0x7ff7733a1003]
-	(No symbol) [0x0x7ff7733695d1]
-	(No symbol) [0x0x7ff77336a3f3]
-	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
-	GetHandleVerifier [0x0x7ff773857f3a+2936554]
-	GetHandleVerifier [0x0x7ff773878977+3070247]
-	GetHandleVerifier [0x0x7ff7735b83ce+185214]
-	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
-	GetHandleVerifier [0x0x7ff7735a7b24+117460]
-	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
-	GetHandleVerifier [0x0x7ff77358dbb8+11112]
+	GetHandleVerifier [0x0x7ff64dd7e8e5+80021]
+	GetHandleVerifier [0x0x7ff64dd7e940+80112]
+	(No symbol) [0x0x7ff64db0060f]
+	(No symbol) [0x0x7ff64db58854]
+	(No symbol) [0x0x7ff64db58b1c]
+	(No symbol) [0x0x7ff64dbac927]
+	(No symbol) [0x0x7ff64db8126f]
+	(No symbol) [0x0x7ff64dba968a]
+	(No symbol) [0x0x7ff64db81003]
+	(No symbol) [0x0x7ff64db495d1]
+	(No symbol) [0x0x7ff64db4a3f3]
+	GetHandleVerifier [0x0x7ff64e03dc7d+2960429]
+	GetHandleVerifier [0x0x7ff64e037f3a+2936554]
+	GetHandleVerifier [0x0x7ff64e058977+3070247]
+	GetHandleVerifier [0x0x7ff64dd983ce+185214]
+	GetHandleVerifier [0x0x7ff64dd9fe1f+216527]
+	GetHandleVerifier [0x0x7ff64dd87b24+117460]
+	GetHandleVerifier [0x0x7ff64dd87cdf+117903]
+	GetHandleVerifier [0x0x7ff64dd6dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
@@ -2985,27 +2985,27 @@
       <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.122); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff77359e8e5+80021]
-	GetHandleVerifier [0x0x7ff77359e940+80112]
-	(No symbol) [0x0x7ff77332060f]
-	(No symbol) [0x0x7ff773378854]
-	(No symbol) [0x0x7ff773378b1c]
-	(No symbol) [0x0x7ff7733cc927]
-	(No symbol) [0x0x7ff7733a126f]
-	(No symbol) [0x0x7ff7733c968a]
-	(No symbol) [0x0x7ff7733a1003]
-	(No symbol) [0x0x7ff7733695d1]
-	(No symbol) [0x0x7ff77336a3f3]
-	GetHandleVerifier [0x0x7ff77385dc7d+2960429]
-	GetHandleVerifier [0x0x7ff773857f3a+2936554]
-	GetHandleVerifier [0x0x7ff773878977+3070247]
-	GetHandleVerifier [0x0x7ff7735b83ce+185214]
-	GetHandleVerifier [0x0x7ff7735bfe1f+216527]
-	GetHandleVerifier [0x0x7ff7735a7b24+117460]
-	GetHandleVerifier [0x0x7ff7735a7cdf+117903]
-	GetHandleVerifier [0x0x7ff77358dbb8+11112]
+	GetHandleVerifier [0x0x7ff64dd7e8e5+80021]
+	GetHandleVerifier [0x0x7ff64dd7e940+80112]
+	(No symbol) [0x0x7ff64db0060f]
+	(No symbol) [0x0x7ff64db58854]
+	(No symbol) [0x0x7ff64db58b1c]
+	(No symbol) [0x0x7ff64dbac927]
+	(No symbol) [0x0x7ff64db8126f]
+	(No symbol) [0x0x7ff64dba968a]
+	(No symbol) [0x0x7ff64db81003]
+	(No symbol) [0x0x7ff64db495d1]
+	(No symbol) [0x0x7ff64db4a3f3]
+	GetHandleVerifier [0x0x7ff64e03dc7d+2960429]
+	GetHandleVerifier [0x0x7ff64e037f3a+2936554]
+	GetHandleVerifier [0x0x7ff64e058977+3070247]
+	GetHandleVerifier [0x0x7ff64dd983ce+185214]
+	GetHandleVerifier [0x0x7ff64dd9fe1f+216527]
+	GetHandleVerifier [0x0x7ff64dd87b24+117460]
+	GetHandleVerifier [0x0x7ff64dd87cdf+117903]
+	GetHandleVerifier [0x0x7ff64dd6dbb8+11112]
 	BaseThreadInitThunk [0x0x7ffc6203e8d7+23]
 	RtlUserThreadStart [0x0x7ffc62fac53c+44]
 </t>
